--- a/AtchisonRegime/Outputs/Brazil/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Brazil/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
@@ -1352,13 +1352,13 @@
         <v>45626</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1412669016474817</v>
+        <v>0.1621739701535616</v>
       </c>
     </row>
   </sheetData>
